--- a/Result/profitability/5210.xlsx
+++ b/Result/profitability/5210.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.63</v>
       </c>
       <c r="M2" t="n">
-        <v>0.23125</v>
+        <v>0.3</v>
       </c>
       <c r="N2" t="n">
-        <v>69.96375</v>
+        <v>72.03125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
         <v>97.09999999999999</v>
@@ -780,10 +780,10 @@
         <v>-0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>0.265</v>
+        <v>0.23</v>
       </c>
       <c r="N3" t="n">
-        <v>70.13499999999999</v>
+        <v>71.295</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2075</v>
+        <v>0.23375</v>
       </c>
       <c r="N4" t="n">
-        <v>68.95</v>
+        <v>70.40625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.74</v>
       </c>
       <c r="M5" t="n">
-        <v>0.10875</v>
+        <v>0.13</v>
       </c>
       <c r="N5" t="n">
-        <v>69.21250000000001</v>
+        <v>70.33750000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.10875</v>
+        <v>0.135</v>
       </c>
       <c r="N6" t="n">
-        <v>68.91625000000001</v>
+        <v>70.30875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>0.15375</v>
+        <v>0.11875</v>
       </c>
       <c r="N7" t="n">
-        <v>69.81625</v>
+        <v>70.28</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>-0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08125</v>
+        <v>0.08375000000000002</v>
       </c>
       <c r="N8" t="n">
-        <v>67.73375</v>
+        <v>70.71125000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.11</v>
       </c>
       <c r="M9" t="n">
-        <v>0.065</v>
+        <v>0.06500000000000003</v>
       </c>
       <c r="N9" t="n">
         <v>69.50749999999999</v>
@@ -1645,10 +1645,10 @@
         <v>0.08</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.003749999999999991</v>
+        <v>-0.003749999999999977</v>
       </c>
       <c r="N10" t="n">
-        <v>68.15125</v>
+        <v>68.15124999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.06</v>
       </c>
       <c r="M11" t="n">
-        <v>0.006250000000000009</v>
+        <v>0.006250000000000023</v>
       </c>
       <c r="N11" t="n">
         <v>67.395</v>
@@ -1899,7 +1899,7 @@
         <v>0.19</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02000000000000001</v>
+        <v>0.02000000000000002</v>
       </c>
       <c r="N12" t="n">
         <v>66.08374999999999</v>
@@ -2029,7 +2029,7 @@
         <v>0.1325</v>
       </c>
       <c r="N13" t="n">
-        <v>65.33750000000001</v>
+        <v>65.33749999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5210</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>66</v>
+      </c>
+      <c r="D75" t="n">
+        <v>12</v>
+      </c>
+      <c r="E75" t="n">
+        <v>54</v>
+      </c>
+      <c r="F75" t="n">
+        <v>82.26000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>6</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.97%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>18</v>
+      </c>
+      <c r="J75" t="n">
+        <v>24</v>
+      </c>
+      <c r="K75" t="n">
+        <v>21</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="N75" t="n">
+        <v>71.61750000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.08333333333333348</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>23.82000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4075975359342918</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.888888888888889</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1228501228501229</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
